--- a/data/P1/P1T1_BQ2.xlsx
+++ b/data/P1/P1T1_BQ2.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Moons/單詞複習網素材/data/P1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F918D150-15D0-0C4A-9F79-2538E6DD083F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01552024-ECCE-0D40-833C-7E23557FE620}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="460" windowWidth="24820" windowHeight="15020" xr2:uid="{90F29878-E095-0247-8CA8-B281629F062F}"/>
+    <workbookView xWindow="30920" yWindow="4100" windowWidth="24820" windowHeight="15020" activeTab="1" xr2:uid="{90F29878-E095-0247-8CA8-B281629F062F}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
+    <sheet name="工作表2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
   <si>
     <t>word</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -157,13 +158,56 @@
   </si>
   <si>
     <t>夜晚</t>
+  </si>
+  <si>
+    <t>Out in the garden up in the tree, there are six red butterflies.</t>
+  </si>
+  <si>
+    <t>There are five green lizards.</t>
+  </si>
+  <si>
+    <t>There are four brown birds.</t>
+  </si>
+  <si>
+    <t>There are three purple cats and two yellow dogs.</t>
+  </si>
+  <si>
+    <t>There are twenty animals.</t>
+  </si>
+  <si>
+    <t>chinese</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sentence</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在花園外的樹上，有六隻紅色的蝴蝶。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>有五隻綠色的蜥蜴。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>有四隻棕色的鳥。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>有三隻紫色的貓和兩隻黃色的狗。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>總共有二十隻動物。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -200,6 +244,12 @@
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -223,7 +273,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -235,6 +285,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -822,4 +878,66 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C218151-EEAE-E947-9EDD-2AFBCF5DEF80}">
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="60.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="16">
+      <c r="A1" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="16">
+      <c r="A2" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="16">
+      <c r="A3" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="16">
+      <c r="A4" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="16">
+      <c r="A5" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="16">
+      <c r="A6" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" t="s">
+        <v>54</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/P1/P1T1_BQ2.xlsx
+++ b/data/P1/P1T1_BQ2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Moons/單詞複習網素材/data/P1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01552024-ECCE-0D40-833C-7E23557FE620}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{587D8E8C-223A-C142-A985-3FF4FED4F47D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30920" yWindow="4100" windowWidth="24820" windowHeight="15020" activeTab="1" xr2:uid="{90F29878-E095-0247-8CA8-B281629F062F}"/>
+    <workbookView xWindow="33920" yWindow="6260" windowWidth="24820" windowHeight="15020" xr2:uid="{90F29878-E095-0247-8CA8-B281629F062F}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="82">
   <si>
     <t>word</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -201,13 +201,94 @@
   <si>
     <t>總共有二十隻動物。</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>phonetics</t>
+  </si>
+  <si>
+    <t>syllable</t>
+  </si>
+  <si>
+    <t>/ˈjeləʊ/</t>
+  </si>
+  <si>
+    <t>yel-low</t>
+  </si>
+  <si>
+    <t>/blæk/</t>
+  </si>
+  <si>
+    <t>--</t>
+  </si>
+  <si>
+    <t>/pɪŋk/</t>
+  </si>
+  <si>
+    <t>/skaɪ/</t>
+  </si>
+  <si>
+    <t>/red/</t>
+  </si>
+  <si>
+    <t>/braʊn/</t>
+  </si>
+  <si>
+    <t>/dɑːk/</t>
+  </si>
+  <si>
+    <t>/sʌn/</t>
+  </si>
+  <si>
+    <t>/bluː/</t>
+  </si>
+  <si>
+    <t>/waɪt/</t>
+  </si>
+  <si>
+    <t>/laɪt/</t>
+  </si>
+  <si>
+    <t>/moon/</t>
+  </si>
+  <si>
+    <t>/ɡriːn/</t>
+  </si>
+  <si>
+    <t>/ɡreɪ/</t>
+  </si>
+  <si>
+    <t>/mɪks/</t>
+  </si>
+  <si>
+    <t>/klaʊdz/</t>
+  </si>
+  <si>
+    <t>/ˈpɜːpl/</t>
+  </si>
+  <si>
+    <t>pur-ple</t>
+  </si>
+  <si>
+    <t>/ˈɒrɪndʒ/</t>
+  </si>
+  <si>
+    <t>or-ange</t>
+  </si>
+  <si>
+    <t>/ˈkreɪɒnz/</t>
+  </si>
+  <si>
+    <t>cray-ons</t>
+  </si>
+  <si>
+    <t>/naɪt/</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -250,6 +331,14 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -259,12 +348,27 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDEE0E3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFDEE0E3"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -273,7 +377,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -291,6 +395,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -606,10 +713,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{527ABE91-7216-BA4F-A91C-2F06E544A41C}">
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -619,10 +732,18 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="3"/>
+      <c r="D1" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>56</v>
+      </c>
       <c r="F1" s="3"/>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -632,8 +753,14 @@
       <c r="C2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="D2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -643,8 +770,14 @@
       <c r="C3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:6">
+      <c r="D3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -654,8 +787,14 @@
       <c r="C4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
+      <c r="D4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -665,8 +804,14 @@
       <c r="C5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
+      <c r="D5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -676,8 +821,14 @@
       <c r="C6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
+      <c r="D6" t="s">
+        <v>63</v>
+      </c>
+      <c r="E6" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -687,8 +838,14 @@
       <c r="C7">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="1:6">
+      <c r="D7" t="s">
+        <v>64</v>
+      </c>
+      <c r="E7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -698,8 +855,14 @@
       <c r="C8">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:6">
+      <c r="D8" t="s">
+        <v>65</v>
+      </c>
+      <c r="E8" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -709,8 +872,14 @@
       <c r="C9">
         <v>2</v>
       </c>
-    </row>
-    <row r="10" spans="1:6">
+      <c r="D9" t="s">
+        <v>66</v>
+      </c>
+      <c r="E9" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -720,8 +889,14 @@
       <c r="C10">
         <v>2</v>
       </c>
-    </row>
-    <row r="11" spans="1:6">
+      <c r="D10" t="s">
+        <v>67</v>
+      </c>
+      <c r="E10" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" t="s">
         <v>21</v>
       </c>
@@ -731,8 +906,14 @@
       <c r="C11">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" spans="1:6">
+      <c r="D11" t="s">
+        <v>68</v>
+      </c>
+      <c r="E11" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" t="s">
         <v>23</v>
       </c>
@@ -742,8 +923,14 @@
       <c r="C12">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:6">
+      <c r="D12" t="s">
+        <v>69</v>
+      </c>
+      <c r="E12" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -753,8 +940,14 @@
       <c r="C13">
         <v>3</v>
       </c>
-    </row>
-    <row r="14" spans="1:6">
+      <c r="D13" t="s">
+        <v>70</v>
+      </c>
+      <c r="E13" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -764,8 +957,14 @@
       <c r="C14">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:6">
+      <c r="D14" t="s">
+        <v>71</v>
+      </c>
+      <c r="E14" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" t="s">
         <v>29</v>
       </c>
@@ -775,8 +974,14 @@
       <c r="C15">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:6">
+      <c r="D15" t="s">
+        <v>72</v>
+      </c>
+      <c r="E15" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" t="s">
         <v>31</v>
       </c>
@@ -786,8 +991,14 @@
       <c r="C16">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:3">
+      <c r="D16" t="s">
+        <v>73</v>
+      </c>
+      <c r="E16" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" t="s">
         <v>33</v>
       </c>
@@ -797,8 +1008,14 @@
       <c r="C17">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="1:3">
+      <c r="D17" t="s">
+        <v>74</v>
+      </c>
+      <c r="E17" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18" t="s">
         <v>35</v>
       </c>
@@ -808,8 +1025,14 @@
       <c r="C18">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="1:3">
+      <c r="D18" t="s">
+        <v>75</v>
+      </c>
+      <c r="E18" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19" t="s">
         <v>37</v>
       </c>
@@ -819,8 +1042,14 @@
       <c r="C19">
         <v>4</v>
       </c>
-    </row>
-    <row r="20" spans="1:3">
+      <c r="D19" t="s">
+        <v>77</v>
+      </c>
+      <c r="E19" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20" t="s">
         <v>39</v>
       </c>
@@ -830,8 +1059,14 @@
       <c r="C20">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="1:3">
+      <c r="D20" t="s">
+        <v>79</v>
+      </c>
+      <c r="E20" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21" t="s">
         <v>41</v>
       </c>
@@ -841,36 +1076,42 @@
       <c r="C21">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="1:3">
+      <c r="D21" t="s">
+        <v>81</v>
+      </c>
+      <c r="E21" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22" s="2"/>
       <c r="B22" s="1"/>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:5">
       <c r="A23" s="2"/>
       <c r="B23" s="1"/>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:5">
       <c r="A24" s="2"/>
       <c r="B24" s="1"/>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:5">
       <c r="A25" s="2"/>
       <c r="B25" s="1"/>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:5">
       <c r="A26" s="2"/>
       <c r="B26" s="1"/>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:5">
       <c r="A27" s="2"/>
       <c r="B27" s="1"/>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:5">
       <c r="A28" s="2"/>
       <c r="B28" s="1"/>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:5">
       <c r="A29" s="2"/>
       <c r="B29" s="1"/>
     </row>

--- a/data/P1/P1T1_BQ2.xlsx
+++ b/data/P1/P1T1_BQ2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Moons/單詞複習網素材/data/P1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/homes/ximonlam/Mac/單詞複習網素材/English/data/P1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{587D8E8C-223A-C142-A985-3FF4FED4F47D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7050C94-B9F1-C947-9A97-8B899DDB0D11}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33920" yWindow="6260" windowWidth="24820" windowHeight="15020" xr2:uid="{90F29878-E095-0247-8CA8-B281629F062F}"/>
+    <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" xr2:uid="{90F29878-E095-0247-8CA8-B281629F062F}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="103">
   <si>
     <t>word</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -282,6 +282,70 @@
   </si>
   <si>
     <t>/naɪt/</t>
+  </si>
+  <si>
+    <t>the color of bananas and sun</t>
+  </si>
+  <si>
+    <t>a very dark color with no light</t>
+  </si>
+  <si>
+    <t>light red color</t>
+  </si>
+  <si>
+    <t>the big blue space above our heads</t>
+  </si>
+  <si>
+    <t>bright color like apples and fire</t>
+  </si>
+  <si>
+    <t>color of wood and chocolate</t>
+  </si>
+  <si>
+    <t>not bright, little light</t>
+  </si>
+  <si>
+    <t>bright hot star that gives us light in daytime</t>
+  </si>
+  <si>
+    <t>color of the sky and sea</t>
+  </si>
+  <si>
+    <t>light color like snow</t>
+  </si>
+  <si>
+    <t>bright, can help us see clearly</t>
+  </si>
+  <si>
+    <t>bright round thing we see at night sky</t>
+  </si>
+  <si>
+    <t>color of grass and leaves</t>
+  </si>
+  <si>
+    <t>color between black and white</t>
+  </si>
+  <si>
+    <t>put two or more colors together</t>
+  </si>
+  <si>
+    <t>white soft shapes floating in the sky</t>
+  </si>
+  <si>
+    <t>color made by red and blue</t>
+  </si>
+  <si>
+    <t>color of oranges, mix of red and yellow</t>
+  </si>
+  <si>
+    <t>colorful sticks for drawing pictures</t>
+  </si>
+  <si>
+    <t>dark time after sunset, before morning</t>
+  </si>
+  <si>
+    <t>English explanation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -377,7 +441,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -397,6 +461,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -720,6 +787,7 @@
     <col min="3" max="3" width="4.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="38.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -738,7 +806,9 @@
       <c r="E1" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="F1" s="3"/>
+      <c r="F1" s="7" t="s">
+        <v>102</v>
+      </c>
       <c r="G1" s="3"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
@@ -759,6 +829,9 @@
       <c r="E2" t="s">
         <v>58</v>
       </c>
+      <c r="F2" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
@@ -776,6 +849,9 @@
       <c r="E3" t="s">
         <v>60</v>
       </c>
+      <c r="F3" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
@@ -793,6 +869,9 @@
       <c r="E4" t="s">
         <v>60</v>
       </c>
+      <c r="F4" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
@@ -810,6 +889,9 @@
       <c r="E5" t="s">
         <v>60</v>
       </c>
+      <c r="F5" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
@@ -827,6 +909,9 @@
       <c r="E6" t="s">
         <v>60</v>
       </c>
+      <c r="F6" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
@@ -844,6 +929,9 @@
       <c r="E7" t="s">
         <v>60</v>
       </c>
+      <c r="F7" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
@@ -861,6 +949,9 @@
       <c r="E8" t="s">
         <v>60</v>
       </c>
+      <c r="F8" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
@@ -878,6 +969,9 @@
       <c r="E9" t="s">
         <v>60</v>
       </c>
+      <c r="F9" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
@@ -895,6 +989,9 @@
       <c r="E10" t="s">
         <v>60</v>
       </c>
+      <c r="F10" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
@@ -912,6 +1009,9 @@
       <c r="E11" t="s">
         <v>60</v>
       </c>
+      <c r="F11" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
@@ -929,6 +1029,9 @@
       <c r="E12" t="s">
         <v>60</v>
       </c>
+      <c r="F12" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
@@ -946,6 +1049,9 @@
       <c r="E13" t="s">
         <v>60</v>
       </c>
+      <c r="F13" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
@@ -963,6 +1069,9 @@
       <c r="E14" t="s">
         <v>60</v>
       </c>
+      <c r="F14" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
@@ -980,6 +1089,9 @@
       <c r="E15" t="s">
         <v>60</v>
       </c>
+      <c r="F15" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
@@ -997,8 +1109,11 @@
       <c r="E16" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="17" spans="1:5">
+      <c r="F16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17" t="s">
         <v>33</v>
       </c>
@@ -1014,8 +1129,11 @@
       <c r="E17" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="18" spans="1:5">
+      <c r="F17" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18" t="s">
         <v>35</v>
       </c>
@@ -1031,8 +1149,11 @@
       <c r="E18" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="19" spans="1:5">
+      <c r="F18" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19" t="s">
         <v>37</v>
       </c>
@@ -1048,8 +1169,11 @@
       <c r="E19" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="20" spans="1:5">
+      <c r="F19" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20" t="s">
         <v>39</v>
       </c>
@@ -1065,8 +1189,11 @@
       <c r="E20" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="21" spans="1:5">
+      <c r="F20" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21" t="s">
         <v>41</v>
       </c>
@@ -1082,36 +1209,39 @@
       <c r="E21" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="22" spans="1:5">
+      <c r="F21" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
       <c r="A22" s="2"/>
       <c r="B22" s="1"/>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:6">
       <c r="A23" s="2"/>
       <c r="B23" s="1"/>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:6">
       <c r="A24" s="2"/>
       <c r="B24" s="1"/>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:6">
       <c r="A25" s="2"/>
       <c r="B25" s="1"/>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:6">
       <c r="A26" s="2"/>
       <c r="B26" s="1"/>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:6">
       <c r="A27" s="2"/>
       <c r="B27" s="1"/>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:6">
       <c r="A28" s="2"/>
       <c r="B28" s="1"/>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:6">
       <c r="A29" s="2"/>
       <c r="B29" s="1"/>
     </row>
